--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-04).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-04).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>22</t>
+    <t>18</t>
   </si>
   <si>
-    <t>R$ 9.012,89</t>
+    <t>R$ 8.996,40</t>
   </si>
   <si>
-    <t>96.4</t>
+    <t>96.3</t>
   </si>
   <si>
     <t>64.6</t>
   </si>
   <si>
-    <t>6.27</t>
+    <t>6.31</t>
   </si>
   <si>
-    <t>20.8</t>
+    <t>21.0</t>
   </si>
   <si>
-    <t>7.6</t>
+    <t>7.8</t>
   </si>
   <si>
     <t>6.4</t>
   </si>
   <si>
-    <t>30.1%</t>
+    <t>30.4%</t>
   </si>
   <si>
     <t>16.0%</t>
@@ -5016,7 +5016,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5046,14 +5046,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>11943.08</v>
+      </c>
+      <c r="N24" s="6">
+        <v>133</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>12.736153846153847</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>29.991754736842104</v>
+      </c>
+      <c r="R24" s="8">
+        <v>8.6907021052631581</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.031578947368421054</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6840,7 +6852,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6870,14 +6882,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>7837.46</v>
+      </c>
+      <c r="N36" s="6">
+        <v>130</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>5.0628787878787875</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>30.556515454545455</v>
+      </c>
+      <c r="R36" s="8">
+        <v>19.342834579439252</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.29999999999999999</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9129,7 +9153,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9159,14 +9183,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1200.3399999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>13</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.0051307692307692</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>27.836660000000002</v>
+      </c>
+      <c r="R51" s="8">
+        <v>16.449999999999999</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -14831,7 +14867,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14859,14 +14895,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>11838.059999999999</v>
+      </c>
+      <c r="N89" s="6">
+        <v>106</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>10.432857142857143</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>34.757843137254902</v>
+      </c>
+      <c r="R89" s="8">
+        <v>20.029251020408164</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.058823529411764705</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
